--- a/data/trans_dic/P2A_lim_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_lim_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,18</t>
+          <t>3,68; 7,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,28; 11,94</t>
+          <t>7,13; 12,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,97</t>
+          <t>6,61; 11,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,97; 17,02</t>
+          <t>11,82; 17,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,18</t>
+          <t>3,79; 7,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,07; 14,41</t>
+          <t>9,17; 13,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,06; 11,58</t>
+          <t>6,96; 11,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,36; 15,45</t>
+          <t>10,42; 15,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 6,67</t>
+          <t>4,17; 6,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,83; 12,25</t>
+          <t>8,91; 12,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,5; 10,71</t>
+          <t>7,3; 10,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,85; 15,61</t>
+          <t>11,86; 15,55</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,95</t>
+          <t>5,42; 8,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,01; 11,99</t>
+          <t>8,04; 12,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 8,54</t>
+          <t>5,25; 8,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,39; 15,34</t>
+          <t>5,77; 15,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 9,65</t>
+          <t>6,16; 9,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,14; 14,32</t>
+          <t>10,13; 14,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 10,79</t>
+          <t>6,91; 10,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,31; 18,14</t>
+          <t>14,31; 18,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 8,68</t>
+          <t>6,26; 8,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,7; 12,46</t>
+          <t>9,54; 12,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,67; 9,23</t>
+          <t>6,63; 9,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 15,68</t>
+          <t>8,9; 15,68</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 9,1</t>
+          <t>4,91; 9,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 10,76</t>
+          <t>6,54; 10,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,97</t>
+          <t>2,92; 6,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,7; 18,6</t>
+          <t>12,96; 18,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 10,69</t>
+          <t>6,62; 10,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,8; 12,53</t>
+          <t>7,63; 12,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,86</t>
+          <t>4,91; 8,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,88; 62,45</t>
+          <t>13,92; 68,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,22</t>
+          <t>6,37; 9,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 10,92</t>
+          <t>7,66; 10,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 6,75</t>
+          <t>4,35; 6,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,48; 53,8</t>
+          <t>14,64; 52,56</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,7; 9,12</t>
+          <t>5,65; 8,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,96; 12,29</t>
+          <t>8,08; 12,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 10,8</t>
+          <t>6,81; 10,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,81; 14,04</t>
+          <t>9,71; 14,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,85; 11,77</t>
+          <t>7,92; 11,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,31; 14,43</t>
+          <t>10,27; 14,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,08; 11,94</t>
+          <t>7,91; 11,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,28; 13,4</t>
+          <t>9,23; 13,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,38; 9,86</t>
+          <t>7,37; 9,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,78; 12,83</t>
+          <t>9,63; 12,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,96; 10,52</t>
+          <t>7,91; 10,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,99; 13,25</t>
+          <t>9,98; 13,09</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 7,58</t>
+          <t>5,81; 7,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 10,68</t>
+          <t>8,47; 10,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,06</t>
+          <t>6,12; 7,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,22; 14,51</t>
+          <t>9,85; 14,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 9,11</t>
+          <t>7,1; 8,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,46; 12,66</t>
+          <t>10,45; 12,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,77; 9,71</t>
+          <t>7,79; 9,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,52; 33,16</t>
+          <t>13,43; 33,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 8,02</t>
+          <t>6,77; 8,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,8; 11,25</t>
+          <t>9,81; 11,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 8,56</t>
+          <t>7,23; 8,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,02; 27,71</t>
+          <t>13,0; 26,03</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25995; 49826</t>
+          <t>25541; 48757</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51240; 84023</t>
+          <t>50177; 84425</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44235; 74022</t>
+          <t>44628; 74848</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75882; 107835</t>
+          <t>74892; 109259</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26712; 49422</t>
+          <t>26084; 49306</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63228; 100476</t>
+          <t>63923; 96861</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47512; 77905</t>
+          <t>46814; 76699</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>74667; 111298</t>
+          <t>75057; 111678</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58042; 92147</t>
+          <t>57696; 89975</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>123719; 171580</t>
+          <t>124747; 172209</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>101104; 144297</t>
+          <t>98442; 141061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>160448; 211343</t>
+          <t>160636; 210579</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54348; 85914</t>
+          <t>52051; 85439</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81340; 121743</t>
+          <t>81641; 123025</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52414; 86704</t>
+          <t>53328; 86541</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76102; 182639</t>
+          <t>68699; 180860</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59036; 93460</t>
+          <t>59615; 92896</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>104630; 147852</t>
+          <t>104555; 146979</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74502; 112192</t>
+          <t>71843; 111876</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>136120; 172579</t>
+          <t>136172; 172405</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>119071; 167380</t>
+          <t>120757; 167826</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>198614; 255277</t>
+          <t>195313; 255039</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>137151; 189607</t>
+          <t>136221; 191078</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>188535; 335774</t>
+          <t>190735; 335838</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33645; 61316</t>
+          <t>33115; 60755</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49260; 81535</t>
+          <t>49565; 83047</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20700; 44776</t>
+          <t>21867; 46175</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88635; 129803</t>
+          <t>90423; 130608</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44847; 72987</t>
+          <t>45165; 74288</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60591; 97349</t>
+          <t>59300; 97167</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38859; 69222</t>
+          <t>38377; 69031</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>129421; 582321</t>
+          <t>129761; 642330</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>85899; 125068</t>
+          <t>86358; 127431</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>118762; 167651</t>
+          <t>117490; 167571</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66529; 103331</t>
+          <t>66660; 105211</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>236134; 877054</t>
+          <t>238604; 856856</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>53591; 85705</t>
+          <t>53108; 83658</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75388; 116387</t>
+          <t>76467; 115841</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64561; 101302</t>
+          <t>63888; 98207</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>89763; 128455</t>
+          <t>88827; 129483</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>81271; 121863</t>
+          <t>82036; 121621</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>108217; 151541</t>
+          <t>107869; 152093</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84339; 124615</t>
+          <t>82542; 124512</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>101293; 146198</t>
+          <t>100769; 148845</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>145737; 194836</t>
+          <t>145589; 192652</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>195368; 256098</t>
+          <t>192319; 252513</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>157664; 208493</t>
+          <t>156725; 211929</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>200369; 265788</t>
+          <t>200317; 262684</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>189845; 247810</t>
+          <t>189776; 248188</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>291937; 365686</t>
+          <t>290109; 363057</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>207562; 272160</t>
+          <t>206871; 269362</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>351263; 498687</t>
+          <t>338505; 500210</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>241531; 307359</t>
+          <t>239778; 302984</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>372104; 450408</t>
+          <t>371795; 454340</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>274838; 343545</t>
+          <t>275698; 343640</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>499800; 1225374</t>
+          <t>496321; 1231422</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>448730; 532442</t>
+          <t>449897; 534914</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>683949; 785386</t>
+          <t>684420; 792609</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>501359; 591663</t>
+          <t>500086; 596343</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>928987; 1976213</t>
+          <t>927262; 1857005</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_lim_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_lim_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,03</t>
+          <t>3,64; 6,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,13; 12,0</t>
+          <t>7,26; 11,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,61; 11,09</t>
+          <t>6,34; 10,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,82; 17,24</t>
+          <t>11,4; 16,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,16</t>
+          <t>4,09; 7,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,17; 13,9</t>
+          <t>8,99; 14,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 11,4</t>
+          <t>6,99; 11,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,42; 15,5</t>
+          <t>12,17; 16,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,51</t>
+          <t>4,22; 6,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,91; 12,3</t>
+          <t>8,78; 12,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 10,47</t>
+          <t>7,42; 10,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,86; 15,55</t>
+          <t>12,36; 15,74</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,9</t>
+          <t>5,46; 8,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,04; 12,11</t>
+          <t>8,12; 12,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,52</t>
+          <t>5,29; 8,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 15,19</t>
+          <t>11,77; 16,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,16; 9,59</t>
+          <t>6,09; 9,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,13; 14,24</t>
+          <t>10,15; 14,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 10,76</t>
+          <t>7,21; 11,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,31; 18,12</t>
+          <t>14,12; 17,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,26; 8,7</t>
+          <t>6,32; 8,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,54; 12,45</t>
+          <t>9,76; 12,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 9,3</t>
+          <t>6,56; 9,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,9; 15,68</t>
+          <t>13,67; 16,5</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 9,02</t>
+          <t>4,78; 8,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,54; 10,96</t>
+          <t>6,56; 10,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 6,16</t>
+          <t>2,91; 5,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,96; 18,72</t>
+          <t>12,82; 18,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,62; 10,88</t>
+          <t>6,65; 10,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 12,5</t>
+          <t>7,85; 12,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 8,84</t>
+          <t>4,98; 8,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,92; 68,89</t>
+          <t>13,87; 18,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 9,39</t>
+          <t>6,24; 9,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,66; 10,92</t>
+          <t>7,72; 10,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 6,87</t>
+          <t>4,41; 6,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,64; 52,56</t>
+          <t>13,91; 17,42</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 8,9</t>
+          <t>5,67; 8,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,08; 12,24</t>
+          <t>8,28; 12,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,47</t>
+          <t>6,91; 10,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,71; 14,15</t>
+          <t>9,43; 13,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,92; 11,74</t>
+          <t>8,0; 11,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,27; 14,48</t>
+          <t>10,33; 14,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,91; 11,93</t>
+          <t>8,0; 11,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 13,64</t>
+          <t>10,67; 14,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,75</t>
+          <t>7,4; 9,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,63; 12,65</t>
+          <t>9,72; 12,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,91; 10,7</t>
+          <t>7,98; 10,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,98; 13,09</t>
+          <t>10,74; 13,24</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 7,6</t>
+          <t>5,79; 7,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 10,6</t>
+          <t>8,52; 10,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,12; 7,97</t>
+          <t>6,06; 7,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,85; 14,55</t>
+          <t>12,22; 14,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,98</t>
+          <t>7,24; 9,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,45; 12,78</t>
+          <t>10,45; 12,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 9,71</t>
+          <t>7,8; 9,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,43; 33,32</t>
+          <t>13,53; 15,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,77; 8,05</t>
+          <t>6,75; 8,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,81; 11,36</t>
+          <t>9,8; 11,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,23; 8,62</t>
+          <t>7,26; 8,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,0; 26,03</t>
+          <t>13,26; 14,85</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90856</t>
+          <t>95127</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>95133</t>
+          <t>102528</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>185989</t>
+          <t>197655</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25541; 48757</t>
+          <t>25296; 47841</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50177; 84425</t>
+          <t>51107; 83186</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44628; 74848</t>
+          <t>42758; 73717</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74892; 109259</t>
+          <t>78512; 113506</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26084; 49306</t>
+          <t>28145; 49185</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63923; 96861</t>
+          <t>62699; 97757</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46814; 76699</t>
+          <t>47006; 76585</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>75057; 111678</t>
+          <t>88783; 118512</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>57696; 89975</t>
+          <t>58290; 91284</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>124747; 172209</t>
+          <t>122945; 170264</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>98442; 141061</t>
+          <t>100022; 141741</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>160636; 210579</t>
+          <t>175260; 223212</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>136024</t>
+          <t>147668</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>152490</t>
+          <t>168879</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>288513</t>
+          <t>316546</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52051; 85439</t>
+          <t>52404; 85319</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81641; 123025</t>
+          <t>82455; 122680</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53328; 86541</t>
+          <t>53719; 87853</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68699; 180860</t>
+          <t>123167; 175146</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59615; 92896</t>
+          <t>58933; 94505</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>104555; 146979</t>
+          <t>104809; 147261</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71843; 111876</t>
+          <t>75002; 114429</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>136172; 172405</t>
+          <t>150155; 189981</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120757; 167826</t>
+          <t>121810; 168751</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>195313; 255039</t>
+          <t>199964; 255734</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>136221; 191078</t>
+          <t>134722; 188821</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>190735; 335838</t>
+          <t>288441; 348025</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108216</t>
+          <t>121041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>312354</t>
+          <t>130293</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>420570</t>
+          <t>251334</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33115; 60755</t>
+          <t>32232; 60499</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49565; 83047</t>
+          <t>49688; 83223</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21867; 46175</t>
+          <t>21852; 44275</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90423; 130608</t>
+          <t>101629; 144594</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45165; 74288</t>
+          <t>45386; 74089</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59300; 97167</t>
+          <t>61017; 96467</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38377; 69031</t>
+          <t>38864; 69548</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>129761; 642330</t>
+          <t>112522; 153155</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>86358; 127431</t>
+          <t>84654; 125558</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117490; 167571</t>
+          <t>118473; 166148</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66660; 105211</t>
+          <t>67521; 106076</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>238604; 856856</t>
+          <t>223135; 279461</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107110</t>
+          <t>110874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>126650</t>
+          <t>137557</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>233760</t>
+          <t>248431</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>53108; 83658</t>
+          <t>53241; 83122</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>76467; 115841</t>
+          <t>78422; 117297</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63888; 98207</t>
+          <t>64786; 98889</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88827; 129483</t>
+          <t>92183; 132918</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>82036; 121621</t>
+          <t>82871; 122970</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>107869; 152093</t>
+          <t>108428; 151533</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82542; 124512</t>
+          <t>83511; 124556</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100769; 148845</t>
+          <t>119029; 156708</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>145589; 192652</t>
+          <t>146074; 196955</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>192319; 252513</t>
+          <t>194058; 254147</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>156725; 211929</t>
+          <t>158149; 208997</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>200317; 262684</t>
+          <t>224675; 277131</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>442206</t>
+          <t>474711</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>686628</t>
+          <t>539257</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1128833</t>
+          <t>1013967</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>189776; 248188</t>
+          <t>189238; 250372</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>290109; 363057</t>
+          <t>291578; 364317</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>206871; 269362</t>
+          <t>204528; 268352</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>338505; 500210</t>
+          <t>428364; 515490</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>239778; 302984</t>
+          <t>244338; 305926</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>371795; 454340</t>
+          <t>371725; 453782</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>275698; 343640</t>
+          <t>275777; 345368</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>496321; 1231422</t>
+          <t>503319; 576475</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>449897; 534914</t>
+          <t>448197; 532244</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>684420; 792609</t>
+          <t>683989; 793306</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>500086; 596343</t>
+          <t>501779; 593632</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>927262; 1857005</t>
+          <t>957866; 1073169</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_lim_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_lim_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica) (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica) (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
